--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_299_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_299_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0902</v>
+        <v>2.8578</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6939</v>
+        <v>3.4279</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6037</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>2.6621</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2321</v>
+        <v>0.9996</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5716</v>
+        <v>1.3056</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3396</v>
+        <v>-0.306</v>
       </c>
       <c r="V2" t="n">
         <v>0.8197</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4102</v>
+        <v>1.3949</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3434</v>
+        <v>1.9143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0668</v>
+        <v>-0.5194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3089</v>
+        <v>-0.6171</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5197000000000001</v>
+        <v>-1.1992</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2108</v>
+        <v>0.5821</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5412</v>
+        <v>1.2596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5412</v>
+        <v>0.3564</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.9032</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2323</v>
+        <v>-1.8766</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0216</v>
+        <v>-1.5556</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2108</v>
+        <v>-0.3211</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8694</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8022</v>
+        <v>-0.3299</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0672</v>
+        <v>-0.1968</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.5387</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2012</v>
+        <v>1.0392</v>
       </c>
       <c r="E4" t="n">
-        <v>1.112</v>
+        <v>0.8716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0892</v>
+        <v>0.1676</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6889</v>
+        <v>0.3089</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8127</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1239</v>
+        <v>-0.2108</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3731</v>
+        <v>0.5412</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4468</v>
+        <v>0.5412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0736</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3157</v>
+        <v>-0.2323</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.366</v>
+        <v>-0.0216</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0502</v>
+        <v>-0.2108</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4261</v>
+        <v>0.4984</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4129</v>
+        <v>0.3304</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0132</v>
+        <v>0.168</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4444</v>
+        <v>0.8144</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973</v>
+        <v>-0.1797</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0234</v>
+        <v>-1.6889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2375</v>
+        <v>-1.8127</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2609</v>
+        <v>0.1239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8736</v>
+        <v>-0.3731</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7632</v>
+        <v>-0.4468</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1104</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.897</v>
+        <v>-1.3157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.366</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3713</v>
+        <v>0.0502</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1611</v>
+        <v>0.0393</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7512</v>
+        <v>0.295</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4099</v>
+        <v>-0.2557</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1346</v>
+        <v>0.5313</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0572</v>
+        <v>0.5395</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9227</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6171</v>
+        <v>-0.1593</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1992</v>
+        <v>1.0419</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5821</v>
+        <v>-1.2012</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2596</v>
+        <v>1.6674</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3564</v>
+        <v>2.4941</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9032</v>
+        <v>-0.8267</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8766</v>
+        <v>-1.8268</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5556</v>
+        <v>-1.4522</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3211</v>
+        <v>-0.3746</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7871</v>
+        <v>-0.0953</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.187</v>
+        <v>0.0318</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6001</v>
+        <v>-0.1272</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5387</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1266</v>
+        <v>-0.2639</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8899</v>
+        <v>0.6854</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0165</v>
+        <v>-0.9493</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2235</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.847</v>
+        <v>0.7097</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2363</v>
+        <v>0.0318</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6106</v>
+        <v>0.6778</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5115</v>
+        <v>-0.2969</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6714</v>
+        <v>-1.2606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1598</v>
+        <v>0.9637</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1593</v>
+        <v>-0.0234</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0419</v>
+        <v>0.2375</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2012</v>
+        <v>-0.2609</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6674</v>
+        <v>0.8736</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4941</v>
+        <v>0.7632</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8267</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8268</v>
+        <v>-0.897</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4522</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3746</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1382</v>
+        <v>0.4197</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1791</v>
+        <v>0.0435</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0409</v>
+        <v>0.3763</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8451</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9936</v>
+        <v>-1.2115</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1485</v>
+        <v>0.351</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1592</v>
+        <v>-1.9288</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3193</v>
+        <v>-0.761</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8399</v>
+        <v>-1.1678</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7695</v>
+        <v>-1.1173</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0168</v>
+        <v>0.1008</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7863</v>
+        <v>-1.2181</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3896</v>
+        <v>-0.8116</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3361</v>
+        <v>-0.8618</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0535</v>
+        <v>0.0502</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.3233</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3062</v>
+        <v>-0.2291</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3151</v>
+        <v>-0.9459</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5653</v>
+        <v>-0.9936</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2502</v>
+        <v>0.0477</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9288</v>
+        <v>-1.1592</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.761</v>
+        <v>-0.3193</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1678</v>
+        <v>-0.8399</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1173</v>
+        <v>-0.7695</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1008</v>
+        <v>0.0168</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2181</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8116</v>
+        <v>-0.3896</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8618</v>
+        <v>-0.3361</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0502</v>
+        <v>-0.0535</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.778</v>
+        <v>-0.0187</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.224</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3299</v>
+        <v>0.2054</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0038</v>
+        <v>-2.3559</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2403</v>
+        <v>-1.4579</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7635</v>
+        <v>-0.8979</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8312</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5078</v>
+        <v>1.1558</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4991</v>
+        <v>0.2833</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0069</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1563</v>
+        <v>-3.8457</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4737</v>
+        <v>-3.1631</v>
       </c>
       <c r="F12" t="n">
         <v>-0.6826</v>
@@ -1390,10 +1390,10 @@
         <v>2.5515</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8022</v>
+        <v>1.1127</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4762</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>0.326</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6778</v>
+        <v>-1.9311</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4007999999999998</v>
+        <v>0.3460000000000005</v>
       </c>
       <c r="F13" t="n">
         <v>-2.2772</v>
@@ -1441,7 +1441,7 @@
         <v>-12.0789</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9808</v>
+        <v>-1.980799999999999</v>
       </c>
       <c r="K13" t="n">
         <v>5.849899999999999</v>
@@ -1462,22 +1462,22 @@
         <v>4.638999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.2782</v>
+        <v>-9.278200000000002</v>
       </c>
       <c r="R13" t="n">
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2245</v>
+        <v>3.971200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7131</v>
+        <v>2.4601</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5113</v>
+        <v>1.5112</v>
       </c>
       <c r="V13" t="n">
-        <v>4.683100000000001</v>
+        <v>4.6831</v>
       </c>
       <c r="W13" t="n">
         <v>9.1448</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6779</v>
+        <v>4.5543</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7404</v>
+        <v>1.2685</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9376</v>
+        <v>3.2857</v>
       </c>
       <c r="G14" t="n">
         <v>2.9391</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7183</v>
+        <v>0.5946</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9006</v>
+        <v>0.4288</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1823</v>
+        <v>0.1658</v>
       </c>
       <c r="V14" t="n">
         <v>0.7886</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9162</v>
+        <v>2.4984</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>1.5486</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4161</v>
+        <v>0.9498</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1286</v>
+        <v>2.11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.4502</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0373</v>
+        <v>1.6597</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3858</v>
+        <v>2.5073</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1344</v>
+        <v>1.7344</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2514</v>
+        <v>0.7729</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2572</v>
+        <v>-0.3973</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0431</v>
+        <v>-1.2842</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.214</v>
+        <v>0.8868</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3236</v>
+        <v>0.0147</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3462</v>
+        <v>0.0593</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9774</v>
+        <v>-0.0446</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8243</v>
+        <v>2.2598</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3127</v>
+        <v>1.1462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5116000000000001</v>
+        <v>1.1137</v>
       </c>
       <c r="G16" t="n">
-        <v>2.11</v>
+        <v>1.1286</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4502</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6597</v>
+        <v>1.0373</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5073</v>
+        <v>1.3858</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7344</v>
+        <v>0.1344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7729</v>
+        <v>1.2514</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3973</v>
+        <v>-0.2572</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2842</v>
+        <v>-0.0431</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8868</v>
+        <v>-0.214</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6594</v>
+        <v>0.6673</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1766</v>
+        <v>-0.0077</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4828</v>
+        <v>0.675</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3858</v>
+        <v>2.1264</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3018</v>
+        <v>0.7736</v>
       </c>
       <c r="F17" t="n">
-        <v>1.084</v>
+        <v>1.3528</v>
       </c>
       <c r="G17" t="n">
         <v>2.8224</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.666</v>
+        <v>0.0747</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2302</v>
+        <v>0.4991</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4665</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2044</v>
+        <v>1.9286</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7542</v>
+        <v>0.8721</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4502</v>
+        <v>1.0565</v>
       </c>
       <c r="G18" t="n">
         <v>0.5994</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2353</v>
+        <v>-0.5111</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1766</v>
+        <v>-0.0587</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0587</v>
+        <v>-0.4525</v>
       </c>
       <c r="V18" t="n">
         <v>1.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1389</v>
+        <v>0.265</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7769</v>
+        <v>0.9449</v>
       </c>
       <c r="G19" t="n">
         <v>0.288</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.749</v>
+        <v>-0.3451</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0725</v>
+        <v>0.2405</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1418</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3849</v>
+        <v>-0.427</v>
       </c>
       <c r="E20" t="n">
-        <v>0.25</v>
+        <v>0.4543</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6349</v>
+        <v>-0.8813</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4259</v>
+        <v>1.2135</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0286</v>
+        <v>1.4008</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6027</v>
+        <v>-0.1873</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9364</v>
+        <v>1.8176</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4383</v>
+        <v>1.6336</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5018</v>
+        <v>0.184</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5105</v>
+        <v>-0.604</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5904</v>
+        <v>-0.2327</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1009</v>
+        <v>-0.3713</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8812</v>
+        <v>-0.0659</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>-0.3969</v>
       </c>
       <c r="U20" t="n">
-        <v>0.767</v>
+        <v>0.331</v>
       </c>
       <c r="V20" t="n">
+        <v>-0.6468</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="X20" t="n">
         <v>-1.0722</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5786</v>
+        <v>-0.8948</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3364</v>
+        <v>-0.1039</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9149</v>
+        <v>-0.7909</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2135</v>
+        <v>-0.4259</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4008</v>
+        <v>-2.0286</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1873</v>
+        <v>1.6027</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8176</v>
+        <v>-0.9364</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6336</v>
+        <v>-1.4383</v>
       </c>
       <c r="L21" t="n">
-        <v>0.184</v>
+        <v>0.5018</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.604</v>
+        <v>0.5105</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2327</v>
+        <v>-0.5904</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3713</v>
+        <v>1.1009</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2175</v>
+        <v>0.3714</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5149</v>
+        <v>-0.2396</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2974</v>
+        <v>0.6111</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6468</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4254</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4816</v>
+        <v>-1.3006</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0958</v>
+        <v>0.0507</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3859</v>
+        <v>-1.3513</v>
       </c>
       <c r="G22" t="n">
-        <v>0.032</v>
+        <v>0.9749</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0048</v>
+        <v>1.9351</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0368</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0536</v>
+        <v>1.5287</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0168</v>
+        <v>2.1678</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0368</v>
+        <v>-0.6391</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0216</v>
+        <v>-0.5538</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0216</v>
+        <v>-0.2327</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.3211</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4415</v>
+        <v>-0.5977</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1494</v>
+        <v>-0.0863</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2921</v>
+        <v>-0.5113</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6042</v>
+        <v>-1.3301</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1872</v>
+        <v>0.0222</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.417</v>
+        <v>-1.3523</v>
       </c>
       <c r="G23" t="n">
-        <v>0.119</v>
+        <v>0.032</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1357</v>
+        <v>-0.0048</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0167</v>
+        <v>0.0368</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0368</v>
+        <v>0.0536</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.0168</v>
       </c>
       <c r="L23" t="n">
         <v>0.0368</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0822</v>
+        <v>-0.0216</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1357</v>
+        <v>-0.0216</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0535</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.651</v>
+        <v>-0.2899</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.224</v>
+        <v>-0.0314</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.427</v>
+        <v>-0.2585</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8118</v>
+        <v>-1.3798</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3032</v>
+        <v>-0.1872</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5086</v>
+        <v>-1.1925</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9749</v>
+        <v>0.119</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9351</v>
+        <v>0.1357</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.0167</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5287</v>
+        <v>0.0368</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1678</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6391</v>
+        <v>0.0368</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5538</v>
+        <v>0.0822</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2327</v>
+        <v>0.1357</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3211</v>
+        <v>-0.0535</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1088</v>
+        <v>-0.4266</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4402</v>
+        <v>-0.224</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6686</v>
+        <v>-0.2025</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3306</v>
+        <v>-3.2634</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2746</v>
+        <v>-2.7464</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.056</v>
+        <v>-0.517</v>
       </c>
       <c r="G25" t="n">
         <v>3.4233</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4191</v>
+        <v>-0.3519</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5272</v>
+        <v>0.0553</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9462</v>
+        <v>-0.4072</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.677999999999999</v>
+        <v>5.036800000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>2.418900000000001</v>
+        <v>2.418800000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2591000000000006</v>
+        <v>2.618100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>15.2243</v>
@@ -2458,7 +2458,7 @@
         <v>13.2436</v>
       </c>
       <c r="K26" t="n">
-        <v>8.995399999999998</v>
+        <v>8.9954</v>
       </c>
       <c r="L26" t="n">
         <v>4.2483</v>
@@ -2482,13 +2482,13 @@
         <v>9.2782</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.2245</v>
+        <v>-0.8654999999999998</v>
       </c>
       <c r="T26" t="n">
         <v>-1.5112</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.7132</v>
+        <v>0.6459000000000006</v>
       </c>
       <c r="V26" t="n">
         <v>-4.6831</v>
